--- a/assets/category.xlsx
+++ b/assets/category.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\90915\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\90915\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF16EB9F-AE5E-47E0-A6F2-025A12357BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B426043-68C4-4C4A-93DC-BA102380D177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3165" yWindow="2025" windowWidth="38700" windowHeight="14085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7680" yWindow="2085" windowWidth="25485" windowHeight="12045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="분류체계" sheetId="4" r:id="rId1"/>
@@ -34,11 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="552">
-  <si>
-    <t xml:space="preserve"> 항공기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="549">
   <si>
     <t xml:space="preserve"> 1-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,26 +44,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 조류 충돌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기체 고장 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-2-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기체 결함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-2-2</t>
   </si>
   <si>
@@ -80,33 +64,17 @@
     <t xml:space="preserve"> 1-2-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 고장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기내 재난(화재 등) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-3-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기내 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-3-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기내 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -140,10 +108,6 @@
     <t xml:space="preserve"> 2-2-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공보안</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -152,10 +116,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 좌동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -197,99 +157,39 @@
     <t xml:space="preserve"> 2-5-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기체 충돌(조류, 드론 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-1-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 미확인 비행물체(드론 등) 충돌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 항공전자장비시스템 고장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 착륙, 제동장치 고장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Full Emergency(비상 착륙)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Full Emergency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Local Standby</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 활주로 이착륙 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-5-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 지상 충돌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-5-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 활주로 이탈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-5-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 전복</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-5-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-5-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-5-6</t>
   </si>
   <si>
     <t xml:space="preserve"> 1-5-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> 활주로 이착륙 준사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 지상 이동 중 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-6-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -298,247 +198,87 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 지상 이동 중 준사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 공항 내 항공기 사고/준사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-7-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 공항 내 항공기 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-7-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 공항 내 항공기 준사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 비정상 운항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-8-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 회항(타 공항 간 운항 중인 항공기 비상 착륙)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-8-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> Air Return(출발항공기 회항)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-8-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ramp Return(출발항공기 지상이동 중 주기장 복귀)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-8-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 지연(출발 지연으로 탑승객 장시간 기내 대기 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-8-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 결항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 1-8-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 지상 피랍(납치) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 항공기 지상 피랍(납치)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 항공기 불법 억류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 항공기 폭발물 위협(공항 내)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 항공기 폭파 위협</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 여객터미널 폭파 위협</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-2-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 공항시설 폭파 위협</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-2-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 폭발물 의심물체 발견</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 항공 보안사고 및 대테러</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (테러 위협) 항공기 테러 위협</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (테러 위협) 공항(여객터미널 등) 테러 위협</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (테러 공격) 항공기 테러 공격으로 승객 인명사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (테러 공격) 공항(여객터미널 등) 테러 공격으로 인명사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> (강력 범죄) 항공기내 강력 범죄(흉기 사용)로 승객 피해</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> (강력 범죄) 공항(여객터미널 등) 강력 범죄(흉기 사용) 피해</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> 화생방 테러물질 발견</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-8</t>
   </si>
   <si>
-    <t xml:space="preserve"> 보호구역 불법 진입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-9</t>
   </si>
   <si>
-    <t xml:space="preserve"> 보안검색 불법 방해행위(충돌, 저항 등 소란)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-10</t>
   </si>
   <si>
-    <t xml:space="preserve"> 사어버보안 위협 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-11</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공GPS 전파 혼신(교란) 및 우주전파 재난</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-12</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 항공 보안사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 보안검색시스템</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (T1) 1터미널 보안검색장비시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (T2) 2터미널 보안검색장비시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-4-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 보안검색장비시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 경비보안시스템 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (T1) 1터미널 통합경비보안시스템(ISS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (T2) 2터미널 통합경비보안시스템(ISS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-5-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 경비보안시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 미확인 비행물체 출현(드론 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-6-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -547,442 +287,198 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 항공보안사항</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-7-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 여객터미널</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 체크인시스템</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> (정부) 출입국심사시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-1-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (公社) 공용체크인시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-1-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (DCS) 항공사체크인시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-1-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (SITA, ARINC 등) 체크인글로벌네트워크 장애 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-1-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> (BSM) 수하물정보 송수신(BSM 중계서버 등) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-1-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> (AIRBRS) 수하물탑재확인시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-1-7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 체크인시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 정보시스템</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 통합정보시스템(IIS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-2-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 통합정보연계시스템(EAI) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-2-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 자원배정시스템(RS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-2-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항운영네트워크 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-2-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 정보시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 통신시스템</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-3-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 운항정보표출시스템(FIDS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-3-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항유선전화 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-3-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 주파수공용시스템(TRS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-3-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 안내방송시스템(PAS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-3-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> LTE통합공공망 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-3-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 통신시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 비정상 운영(다중운집, 체객 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 다중운집 인파 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 대규모 운항편 결항, 지연으로 체류여객 발생</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 실종자 발생(아동, 노약자 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널 랜드사이드 내 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널 에어사이드 내 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동(에어사이드) 내 사고 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널 랜드사이드 내 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 3-4-8</t>
   </si>
   <si>
-    <t xml:space="preserve"> 교통시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 교통센터(공항철도역사 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-1-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 공항철도 1터미널역 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-1-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 공항철도 2터미널역 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-1-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) T1교통센터 내 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-1-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) T2교통센터 내 사고(버스터미널 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-1-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 공항철도열차 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 주차시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-2-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 통합교통관리시스템(ITS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-2-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 주차관제시스템(PCFC) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-2-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) T1교통센터 내 단기주차장 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-2-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) T2교통센터 내 단기주차장 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-2-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널 장기주차장 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-2-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널 장기주차장 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 구내교통</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-3-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 공항구역 내 도로시설물 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-3-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널 구내도로 교통사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-3-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널 구내도로 교통사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-3-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> T1, T2 연결도로 교통사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-3-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항외곽도로 교통사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-3-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> 자기부상열차 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 대중교통</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 좌동 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 교통안전사고 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 4-5-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 에어사이드시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 활주로, 유도로</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-1-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 활주로, 유도로(기동지역) 포장 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-1-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 계류장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-2-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 계류장(주기장, 유도선 등) 포장 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-2-2</t>
   </si>
   <si>
@@ -990,903 +486,403 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 탑승교(PBB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-3-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 이동식 탑승교(PBB) 시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 항공유 누유</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 주기장 내 지중 급유피트(하이드란트) 고장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-4-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 급유, 배유작업 중 항공유 누유 발생</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-4-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공기 주기 중이거나 지상 이동 중 누유 발생</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 이동지역 안전사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-5-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 지상조업 안전사고(사상자 발생)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-5-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 지상조업 안전사고(중상자 발생)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-5-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 조류 떼(무리) 대량 출현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-5-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 생동물 탈출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-5-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 이동지역 안전사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 토목시설물 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 5-6-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 공항운영시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 항행안전시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 항공관제통신시설 시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항감시레이더(왕산) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항감시레이더(신불) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항감시레이더(삼목) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항감시레이더(ARTS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항지상감시레이더(ASDE) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> 계기착륙시설(ILS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-8</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항행안전시설(VOR/DME) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-1-9</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 항행안전시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 항공등화시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-2-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 활주로, 유도로(기동지역) 항공등화시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-2-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 계류장(유도선 등) 항공등화시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-2-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 이동지역 항공등화시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-2-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 지상이동안내 및 통제시스템(A-SMGCS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-2-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 시각주기유도시스템(VDGS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-2-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 항공등화시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 전력시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-3-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널(교통센터 포함) 전력 공급 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-3-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동 전력 공급 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-3-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널(교통센터 포함) 전력 공급 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-3-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 전력시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 운송시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 셔틀트레인(1터미널 ⇔ 탑승동) 장애 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-4-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널(교통센터 포함) 승강시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-4-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동 승강시설 장애 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-4-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널(교통센터 포함) 승강시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-4-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 승강시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 건축시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널(교통센터 포함) 건축시설물 파손 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동 건축시설물 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널(교통센터 포함) 건축시설물 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 건축시설물 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널(교통센터 포함) 냉난방시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동 냉난방시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널(교통센터 포함) 냉난방시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-8</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 냉난방시스템 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-9</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널(교통센터 포함) 급배수설비 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-10</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동 급배수설비 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-11</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널(교통센터 포함) 급배수설비 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-12</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 급배수설비 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-13</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널(교통센터 포함) 유틸리티시설(공급배관 등) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-14</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동 유틸리티시설(공급배관 등) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-15</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널(교통센터 포함) 유틸리티시설(공급배관 등) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-5-16</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 유틸리티시설(공급배관 등) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 토목시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-6-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널 랜드사이드 토목시설 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-6-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널 랜드사이드 토목시설 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-6-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 화물터미널지역(물류단지 포함) 토목시설 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-6-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항지원단지(기내식시설 등) 토목시설 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-6-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 첨단항공복합단지 토목시설 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-6-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> 국제업무지역(IBC-1, 2, 3) 토목시설 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-6-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 토목시설 파손</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 기계시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널 출발 수하물처리시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동 출발 수하물처리시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널 출발 수하물처리시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 1터미널 도착 수하물처리시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T1) 탑승동 도착 수하물처리시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> (T2) 2터미널 도착 수하물처리시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 출발(체크인) 수하물처리시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-8</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 도착(입국) 수하물처리시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-9</t>
   </si>
   <si>
-    <t xml:space="preserve"> 중수도시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-10</t>
   </si>
   <si>
-    <t xml:space="preserve"> 중온수공급시설 장애 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-11</t>
   </si>
   <si>
-    <t xml:space="preserve"> 자원회수시설 중앙제어시스템(DCS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-7-12</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 기계시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 급유시설</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-8-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 급유저장시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-8-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 항공유 공급배관 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 6-8-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 급유시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 재난</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 공항재난(화재, 붕괴, 폭발 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (화재) 1터미널(T1교통센터 포함) 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (화재) 탑승동 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (화재) 2터미널(T2교통센터 포함) 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (화재) 화물터미널 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> (화재) 기내식시설 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> (화재) 항공기정비시설 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> (화재) 급유시설 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-8</t>
   </si>
   <si>
-    <t xml:space="preserve"> (화재) 기타 공항시설 화재</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-9</t>
   </si>
   <si>
-    <t xml:space="preserve"> (붕괴) 1터미널(T1교통센터 포함) 구조물 붕괴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-10</t>
   </si>
   <si>
-    <t xml:space="preserve"> (붕괴) 탑승동 구조물 붕괴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-11</t>
   </si>
   <si>
-    <t xml:space="preserve"> (붕괴) 2터미널(T2교통센터 포함) 구조물 붕괴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-12</t>
   </si>
   <si>
-    <t xml:space="preserve"> (붕괴) 화물터미널 구조물 붕괴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-13</t>
   </si>
   <si>
-    <t xml:space="preserve"> (붕괴) 기내식시설 구조물 붕괴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-14</t>
   </si>
   <si>
-    <t xml:space="preserve"> (붕괴) 항공기정비시설 구조물 붕괴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-15</t>
   </si>
   <si>
-    <t xml:space="preserve"> (붕괴) 급유시설 구조물 붕괴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-16</t>
   </si>
   <si>
-    <t xml:space="preserve"> (붕괴) 기타 공항시설 구조물 붕괴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-17</t>
   </si>
   <si>
-    <t xml:space="preserve"> (폭발) 1터미널(T1교통센터 포함) 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-18</t>
   </si>
   <si>
-    <t xml:space="preserve"> (폭발) 탑승동 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-19</t>
   </si>
   <si>
-    <t xml:space="preserve"> (폭발) 2터미널(T2교통센터 포함) 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-20</t>
   </si>
   <si>
-    <t xml:space="preserve"> (폭발) 화물터미널 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-21</t>
   </si>
   <si>
-    <t xml:space="preserve"> (폭발) 기내식시설 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-22</t>
   </si>
   <si>
-    <t xml:space="preserve"> (폭발) 항공기정비시설 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-23</t>
   </si>
   <si>
-    <t xml:space="preserve"> (폭발) 급유시설 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-24</t>
   </si>
   <si>
-    <t xml:space="preserve"> (폭발) 기타 공항시설 폭발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-1-25</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 공항재난 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 자연재난(태풍, 대설 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> (풍수해) 태풍, 호우 등</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> (풍수해) 대설(제방빙)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> (악기상) 저시정(안개)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> (악기상) 낙뢰 등 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> (악기상) 강풍, 윈드시어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-6</t>
   </si>
   <si>
-    <t xml:space="preserve"> (재난) 폭염 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-7</t>
   </si>
   <si>
-    <t xml:space="preserve"> (재난) 한파</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-8</t>
   </si>
   <si>
-    <t xml:space="preserve"> (재난) 지진, 해일 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-9</t>
   </si>
   <si>
-    <t xml:space="preserve"> (재난) 화산 폭발 영향 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-10</t>
   </si>
   <si>
-    <t xml:space="preserve"> (재난) 조류 떼 출현 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-11</t>
   </si>
   <si>
-    <t xml:space="preserve"> 공항 기상 특보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-2-12</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 자연재난</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 항공운송 마비(항공사 파업)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-3-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1895,147 +891,67 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 위험물 사고/준사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 방사능 누출사고 영향</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-4-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 화학물질 누출사고 영향</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-4-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 위험물 사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-4-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 위험물 준사고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 공중보건(감염병)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-5-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 감염병 의심환자 발생 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-5-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 해외 감염병 유입 의심</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-5-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 기타 공중보건 사고 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 구조소방(긴급 출동)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-6-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 화재감시제어시스템(FAS) 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-6-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 소방시설 장애</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-6-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 구조 출동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-6-4</t>
   </si>
   <si>
-    <t xml:space="preserve"> 구급 출동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-6-5</t>
   </si>
   <si>
-    <t xml:space="preserve"> 소방차 지원</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 사회상황(대중교통 파업 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-7-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 대중교통 파업(공항철도 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-7-2</t>
   </si>
   <si>
-    <t xml:space="preserve"> 대중교통 파업(버스 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 7-7-3</t>
   </si>
   <si>
-    <t xml:space="preserve"> 대규모 집회, 시위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 항공기 기동 불능(타이어 과열 파손 등)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 2-3-13</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2065,6 +981,1078 @@
   </si>
   <si>
     <t>소분류 기준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공보안</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여객터미널</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교통시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에어사이드시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항운영시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재난</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기체 충돌(조류, 드론 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기내 재난(화재 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기체 고장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대중교통</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 교통안전사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>토목시설물 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공운송 마비(항공사 파업)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full Emergency(비상 착륙)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주로 이착륙 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 지상 이동 중 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항 내 항공기 사고/준사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 비정상 운항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 지상 피랍(납치)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 폭발물 위협(공항 내)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공 보안사고 및 대테러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보안검색시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경비보안시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미확인 비행물체 출현(드론 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 항공보안사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체크인시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통신시스템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 비정상 운영(다중운집, 체객 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교통센터(공항철도역사 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주차시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구내교통</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주로, 유도로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계류장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탑승교(PBB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공유 누유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동지역 안전사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항행안전시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공등화시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전력시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운송시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건축시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>토목시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급유시설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항재난(화재, 붕괴, 폭발 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자연재난(태풍, 대설 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험물 사고/준사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공중보건(감염병)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구조소방(긴급 출동)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사회상황(대중교통 파업 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조류 충돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미확인 비행물체(드론 등) 충돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기체 결함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공전자장비시스템 고장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>착륙, 제동장치 고장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 기동 불능(타이어 과열 파손 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 고장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기내 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기내 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full Emergency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Local Standby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 지상 충돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주로 이탈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 전복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주로 이착륙 준사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 지상 이동 중 준사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 공항 내 항공기 준사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 공항 내 항공기 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회항(타 공항 간 운항 중인 항공기 비상 착륙)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Air Return(출발항공기 회항)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ramp Return(출발항공기 지상이동 중 주기장 복귀)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지연(출발 지연으로 탑승객 장시간 기내 대기 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 불법 억류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 폭파 위협</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여객터미널 폭파 위협</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 공항시설 폭파 위협</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭발물 의심물체 발견</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(테러 위협) 항공기 테러 위협</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(테러 위협) 공항(여객터미널 등) 테러 위협</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(테러 공격) 항공기 테러 공격으로 승객 인명사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(테러 공격) 공항(여객터미널 등) 테러 공격으로 인명사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(강력 범죄) 항공기내 강력 범죄(흉기 사용)로 승객 피해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(강력 범죄) 공항(여객터미널 등) 강력 범죄(흉기 사용) 피해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화생방 테러물질 발견</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호구역 불법 진입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보안검색 불법 방해행위(충돌, 저항 등 소란)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사어버보안 위협</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공GPS 전파 혼신(교란) 및 우주전파 재난</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 항공 보안사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 보안검색장비시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널 보안검색장비시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 보안검색장비시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 통합경비보안시스템(ISS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널 통합경비보안시스템(ISS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 경비보안시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(정부) 출입국심사시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(公社) 공용체크인시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(DCS) 항공사체크인시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(SITA, ARINC 등) 체크인글로벌네트워크 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(BSM) 수하물정보 송수신(BSM 중계서버 등) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(AIRBRS) 수하물탑재확인시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 체크인시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합정보시스템(IIS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합정보연계시스템(EAI) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원배정시스템(RS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항운영네트워크 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 정보시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운항정보표출시스템(FIDS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항유선전화 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주파수공용시스템(TRS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안내방송시스템(PAS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LTE통합공공망 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 통신시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다중운집 인파 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대규모 운항편 결항, 지연으로 체류여객 발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실종자 발생(아동, 노약자 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 랜드사이드 내 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 에어사이드 내 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동(에어사이드) 내 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널 랜드사이드 내 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 공항철도 1터미널역 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 공항철도 2터미널역 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) T1교통센터 내 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) T2교통센터 내 사고(버스터미널 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항철도열차 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합교통관리시스템(ITS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주차관제시스템(PCFC) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) T1교통센터 내 단기주차장 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) T2교통센터 내 단기주차장 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 장기주차장 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널 장기주차장 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항구역 내 도로시설물 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 구내도로 교통사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널 구내도로 교통사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>T1, T2 연결도로 교통사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항외곽도로 교통사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자기부상열차 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주로, 유도로(기동지역) 포장 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계류장(주기장, 유도선 등) 포장 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식 탑승교(PBB) 시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주기장 내 지중 급유피트(하이드란트) 고장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 급유, 배유작업 중 항공유 누유 발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공기 주기 중이거나 지상 이동 중 누유 발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상조업 안전사고(사상자 발생)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상조업 안전사고(중상자 발생)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조류 떼(무리) 대량 출현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생동물 탈출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 이동지역 안전사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공관제통신시설 시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항감시레이더(왕산) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항감시레이더(신불) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항감시레이더(삼목) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항감시레이더(ARTS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항지상감시레이더(ASDE) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계기착륙시설(ILS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항행안전시설(VOR/DME) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 항행안전시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활주로, 유도로(기동지역) 항공등화시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계류장(유도선 등) 항공등화시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 이동지역 항공등화시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지상이동안내 및 통제시스템(A-SMGCS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시각주기유도시스템(VDGS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 항공등화시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널(교통센터 포함) 전력 공급 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동 전력 공급 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널(교통센터 포함) 전력 공급 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 전력시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">셔틀트레인(1터미널 ⇔ 탑승동) 장애 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널(교통센터 포함) 승강시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동 승강시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널(교통센터 포함) 승강시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 승강시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널(교통센터 포함) 건축시설물 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동 건축시설물 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널(교통센터 포함) 건축시설물 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 건축시설물 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널(교통센터 포함) 냉난방시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동 냉난방시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널(교통센터 포함) 냉난방시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 냉난방시스템 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널(교통센터 포함) 급배수설비 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동 급배수설비 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널(교통센터 포함) 급배수설비 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 급배수설비 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널(교통센터 포함) 유틸리티시설(공급배관 등) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동 유틸리티시설(공급배관 등) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널(교통센터 포함) 유틸리티시설(공급배관 등) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 유틸리티시설(공급배관 등) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 랜드사이드 토목시설 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널 랜드사이드 토목시설 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화물터미널지역(물류단지 포함) 토목시설 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항지원단지(기내식시설 등) 토목시설 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>첨단항공복합단지 토목시설 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국제업무지역(IBC-1, 2, 3) 토목시설 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 토목시설 파손</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 출발 수하물처리시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동 출발 수하물처리시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널 출발 수하물처리시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 1터미널 도착 수하물처리시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T1) 탑승동 도착 수하물처리시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(T2) 2터미널 도착 수하물처리시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 출발(체크인) 수하물처리시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 도착(입국) 수하물처리시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중수도시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중온수공급시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자원회수시설 중앙제어시스템(DCS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 기계시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급유저장시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공유 공급배관 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 급유시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(화재) 1터미널(T1교통센터 포함) 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(화재) 탑승동 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(화재) 2터미널(T2교통센터 포함) 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(화재) 화물터미널 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(화재) 기내식시설 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(화재) 항공기정비시설 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(화재) 급유시설 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(화재) 기타 공항시설 화재</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(붕괴) 1터미널(T1교통센터 포함) 구조물 붕괴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(붕괴) 탑승동 구조물 붕괴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(붕괴) 2터미널(T2교통센터 포함) 구조물 붕괴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(붕괴) 화물터미널 구조물 붕괴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(붕괴) 기내식시설 구조물 붕괴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(붕괴) 항공기정비시설 구조물 붕괴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(붕괴) 급유시설 구조물 붕괴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(붕괴) 기타 공항시설 구조물 붕괴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭발) 1터미널(T1교통센터 포함) 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭발) 탑승동 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭발) 2터미널(T2교통센터 포함) 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭발) 화물터미널 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭발) 기내식시설 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭발) 항공기정비시설 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭발) 급유시설 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(폭발) 기타 공항시설 폭발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 공항재난</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(풍수해) 태풍, 호우 등</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(풍수해) 대설(제방빙)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(악기상) 저시정(안개)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(악기상) 낙뢰 등 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(악기상) 강풍, 윈드시어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(재난) 폭염</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(재난) 한파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(재난) 지진, 해일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(재난) 화산 폭발 영향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(재난) 조류 떼 출현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항 기상 특보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 자연재난</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방사능 누출사고 영향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화학물질 누출사고 영향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 위험물 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 위험물 준사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감염병 의심환자 발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해외 감염병 유입 의심</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기타 공중보건 사고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화재감시제어시스템(FAS) 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방시설 장애</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구조 출동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구급 출동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소방차 지원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대중교통 파업(공항철도 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대중교통 파업(버스 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대규모 집회, 시위</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2073,7 +2061,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -2217,7 +2205,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2235,7 +2223,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2574,22 +2562,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="24.95" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>546</v>
+        <v>275</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>547</v>
+        <v>276</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>548</v>
+        <v>277</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>549</v>
+        <v>278</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>550</v>
+        <v>279</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>551</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="24.95" customHeight="1">
@@ -2597,19 +2585,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>2</v>
-      </c>
       <c r="F2" s="10" t="s">
-        <v>3</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="24.95" customHeight="1">
@@ -2617,19 +2605,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>28</v>
+        <v>282</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>5</v>
+        <v>290</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>45</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="24.95" customHeight="1">
@@ -2637,19 +2625,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>139</v>
+        <v>283</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>14</v>
+        <v>289</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>7</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1">
@@ -2657,19 +2645,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>195</v>
+        <v>284</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>48</v>
+        <v>295</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>46</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="24.95" customHeight="1">
@@ -2677,19 +2665,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>52</v>
+        <v>296</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>47</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="24.95" customHeight="1">
@@ -2697,19 +2685,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>67</v>
+        <v>297</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>543</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="24.95" customHeight="1">
@@ -2717,2023 +2705,2023 @@
         <v>7</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>423</v>
+        <v>287</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>72</v>
+        <v>298</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>12</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="24.95" customHeight="1">
       <c r="C9" s="8" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>16</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="24.95" customHeight="1">
       <c r="C10" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>18</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="24.95" customHeight="1">
       <c r="C11" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>93</v>
+        <v>301</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>49</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="24.95" customHeight="1">
       <c r="C12" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>100</v>
+        <v>302</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>50</v>
+        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="24.95" customHeight="1">
       <c r="C13" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>123</v>
+        <v>303</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>54</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="24.95" customHeight="1">
       <c r="C14" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>128</v>
+        <v>304</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>56</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="24.95" customHeight="1">
       <c r="C15" s="6" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>134</v>
+        <v>305</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>58</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="24.95" customHeight="1">
       <c r="C16" s="6" t="s">
-        <v>136</v>
+        <v>71</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>137</v>
+        <v>306</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>60</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="3:6" ht="24.95" customHeight="1">
       <c r="C17" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>140</v>
+        <v>307</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>62</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="3:6" ht="24.95" customHeight="1">
       <c r="C18" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>154</v>
+        <v>308</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>52</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="3:6" ht="24.95" customHeight="1">
       <c r="C19" s="4" t="s">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>165</v>
+        <v>309</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>65</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="3:6" ht="24.95" customHeight="1">
       <c r="C20" s="4" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>179</v>
+        <v>310</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>67</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="3:6" ht="24.95" customHeight="1">
       <c r="C21" s="4" t="s">
-        <v>196</v>
+        <v>99</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>197</v>
+        <v>311</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>70</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="3:6" ht="24.95" customHeight="1">
       <c r="C22" s="4" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>209</v>
+        <v>312</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>74</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="3:6" ht="24.95" customHeight="1">
       <c r="C23" s="5" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>76</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="3:6" ht="24.95" customHeight="1">
       <c r="C24" s="6" t="s">
-        <v>236</v>
+        <v>119</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>237</v>
+        <v>291</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>80</v>
+        <v>353</v>
       </c>
     </row>
     <row r="25" spans="3:6" ht="24.95" customHeight="1">
       <c r="C25" s="6" t="s">
-        <v>240</v>
+        <v>121</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>82</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="3:6" ht="24.95" customHeight="1">
       <c r="C26" s="4" t="s">
-        <v>244</v>
+        <v>123</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>84</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="3:6" ht="24.95" customHeight="1">
       <c r="C27" s="4" t="s">
-        <v>250</v>
+        <v>126</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>86</v>
+        <v>356</v>
       </c>
     </row>
     <row r="28" spans="3:6" ht="24.95" customHeight="1">
       <c r="C28" s="6" t="s">
-        <v>255</v>
+        <v>129</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>88</v>
+        <v>357</v>
       </c>
     </row>
     <row r="29" spans="3:6" ht="24.95" customHeight="1">
       <c r="C29" s="4" t="s">
-        <v>259</v>
+        <v>131</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>78</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="3:6" ht="24.95" customHeight="1">
       <c r="C30" s="4" t="s">
-        <v>267</v>
+        <v>135</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>268</v>
+        <v>318</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>91</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="3:6" ht="24.95" customHeight="1">
       <c r="C31" s="6" t="s">
-        <v>279</v>
+        <v>141</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>92</v>
+        <v>358</v>
       </c>
     </row>
     <row r="32" spans="3:6" ht="24.95" customHeight="1">
       <c r="C32" s="4" t="s">
-        <v>283</v>
+        <v>143</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>94</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" spans="3:6" ht="24.95" customHeight="1">
       <c r="C33" s="4" t="s">
-        <v>303</v>
+        <v>153</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>95</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34" spans="3:6" ht="24.95" customHeight="1">
       <c r="C34" s="4" t="s">
-        <v>317</v>
+        <v>160</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>97</v>
+        <v>361</v>
       </c>
     </row>
     <row r="35" spans="3:6" ht="24.95" customHeight="1">
       <c r="C35" s="4" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>99</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" spans="3:6" ht="24.95" customHeight="1">
       <c r="C36" s="4" t="s">
-        <v>339</v>
+        <v>171</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>101</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" spans="3:6" ht="24.95" customHeight="1">
       <c r="C37" s="4" t="s">
-        <v>373</v>
+        <v>188</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>102</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" spans="3:6" ht="24.95" customHeight="1">
       <c r="C38" s="4" t="s">
-        <v>389</v>
+        <v>196</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>390</v>
+        <v>325</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>104</v>
+        <v>365</v>
       </c>
     </row>
     <row r="39" spans="3:6" ht="24.95" customHeight="1">
       <c r="C39" s="4" t="s">
-        <v>415</v>
+        <v>209</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>416</v>
+        <v>326</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>106</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="3:6" ht="24.95" customHeight="1">
       <c r="C40" s="4" t="s">
-        <v>424</v>
+        <v>213</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>425</v>
+        <v>327</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>108</v>
+        <v>367</v>
       </c>
     </row>
     <row r="41" spans="3:6" ht="24.95" customHeight="1">
       <c r="C41" s="4" t="s">
-        <v>476</v>
+        <v>239</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>477</v>
+        <v>328</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>110</v>
+        <v>368</v>
       </c>
     </row>
     <row r="42" spans="3:6" ht="24.95" customHeight="1">
       <c r="C42" s="6" t="s">
-        <v>502</v>
+        <v>252</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>503</v>
+        <v>294</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>112</v>
+        <v>369</v>
       </c>
     </row>
     <row r="43" spans="3:6" ht="24.95" customHeight="1">
       <c r="C43" s="4" t="s">
-        <v>505</v>
+        <v>254</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>506</v>
+        <v>329</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>114</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" spans="3:6" ht="24.95" customHeight="1">
       <c r="C44" s="4" t="s">
-        <v>515</v>
+        <v>259</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>516</v>
+        <v>330</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>116</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="3:6" ht="24.95" customHeight="1">
       <c r="C45" s="6" t="s">
-        <v>523</v>
+        <v>263</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>524</v>
+        <v>331</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>118</v>
+        <v>372</v>
       </c>
     </row>
     <row r="46" spans="3:6" ht="24.95" customHeight="1">
       <c r="C46" s="6" t="s">
-        <v>535</v>
+        <v>269</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>536</v>
+        <v>332</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>120</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" spans="3:6" ht="24.95" customHeight="1">
       <c r="E47" s="22" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>545</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" spans="3:6" ht="24.95" customHeight="1">
       <c r="E48" s="21" t="s">
-        <v>544</v>
+        <v>273</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>122</v>
+        <v>374</v>
       </c>
     </row>
     <row r="49" spans="5:6" ht="24.95" customHeight="1">
       <c r="E49" s="21" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>124</v>
+        <v>375</v>
       </c>
     </row>
     <row r="50" spans="5:6" ht="24.95" customHeight="1">
       <c r="E50" s="21" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>125</v>
+        <v>376</v>
       </c>
     </row>
     <row r="51" spans="5:6" ht="24.95" customHeight="1">
       <c r="E51" s="21" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>127</v>
+        <v>377</v>
       </c>
     </row>
     <row r="52" spans="5:6" ht="24.95" customHeight="1">
       <c r="E52" s="21" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>129</v>
+        <v>378</v>
       </c>
     </row>
     <row r="53" spans="5:6" ht="24.95" customHeight="1">
       <c r="E53" s="21" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>130</v>
+        <v>379</v>
       </c>
     </row>
     <row r="54" spans="5:6" ht="24.95" customHeight="1">
       <c r="E54" s="21" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>132</v>
+        <v>380</v>
       </c>
     </row>
     <row r="55" spans="5:6" ht="24.95" customHeight="1">
       <c r="E55" s="21" t="s">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>31</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="5:6" ht="24.95" customHeight="1">
       <c r="E56" s="21" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>31</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57" spans="5:6" ht="24.95" customHeight="1">
       <c r="E57" s="21" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>141</v>
+        <v>381</v>
       </c>
     </row>
     <row r="58" spans="5:6" ht="24.95" customHeight="1">
       <c r="E58" s="21" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>143</v>
+        <v>382</v>
       </c>
     </row>
     <row r="59" spans="5:6" ht="24.95" customHeight="1">
       <c r="E59" s="21" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>145</v>
+        <v>383</v>
       </c>
     </row>
     <row r="60" spans="5:6" ht="24.95" customHeight="1">
       <c r="E60" s="21" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>147</v>
+        <v>384</v>
       </c>
     </row>
     <row r="61" spans="5:6" ht="24.95" customHeight="1">
       <c r="E61" s="21" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>149</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62" spans="5:6" ht="24.95" customHeight="1">
       <c r="E62" s="21" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>151</v>
+        <v>386</v>
       </c>
     </row>
     <row r="63" spans="5:6" ht="24.95" customHeight="1">
       <c r="E63" s="21" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>153</v>
+        <v>387</v>
       </c>
     </row>
     <row r="64" spans="5:6" ht="24.95" customHeight="1">
       <c r="E64" s="21" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>155</v>
+        <v>388</v>
       </c>
     </row>
     <row r="65" spans="5:6" ht="24.95" customHeight="1">
       <c r="E65" s="21" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>157</v>
+        <v>389</v>
       </c>
     </row>
     <row r="66" spans="5:6" ht="24.95" customHeight="1">
       <c r="E66" s="21" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>159</v>
+        <v>390</v>
       </c>
     </row>
     <row r="67" spans="5:6" ht="24.95" customHeight="1">
       <c r="E67" s="21" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>161</v>
+        <v>391</v>
       </c>
     </row>
     <row r="68" spans="5:6" ht="24.95" customHeight="1">
       <c r="E68" s="21" t="s">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>163</v>
+        <v>392</v>
       </c>
     </row>
     <row r="69" spans="5:6" ht="24.95" customHeight="1">
       <c r="E69" s="21" t="s">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>167</v>
+        <v>393</v>
       </c>
     </row>
     <row r="70" spans="5:6" ht="24.95" customHeight="1">
       <c r="E70" s="21" t="s">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>169</v>
+        <v>394</v>
       </c>
     </row>
     <row r="71" spans="5:6" ht="24.95" customHeight="1">
       <c r="E71" s="21" t="s">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>171</v>
+        <v>395</v>
       </c>
     </row>
     <row r="72" spans="5:6" ht="24.95" customHeight="1">
       <c r="E72" s="21" t="s">
-        <v>172</v>
+        <v>87</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>173</v>
+        <v>396</v>
       </c>
     </row>
     <row r="73" spans="5:6" ht="24.95" customHeight="1">
       <c r="E73" s="21" t="s">
-        <v>174</v>
+        <v>88</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>175</v>
+        <v>397</v>
       </c>
     </row>
     <row r="74" spans="5:6" ht="24.95" customHeight="1">
       <c r="E74" s="21" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>177</v>
+        <v>398</v>
       </c>
     </row>
     <row r="75" spans="5:6" ht="24.95" customHeight="1">
       <c r="E75" s="21" t="s">
-        <v>180</v>
+        <v>91</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>181</v>
+        <v>399</v>
       </c>
     </row>
     <row r="76" spans="5:6" ht="24.95" customHeight="1">
       <c r="E76" s="21" t="s">
-        <v>182</v>
+        <v>92</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>183</v>
+        <v>400</v>
       </c>
     </row>
     <row r="77" spans="5:6" ht="24.95" customHeight="1">
       <c r="E77" s="21" t="s">
-        <v>184</v>
+        <v>93</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>185</v>
+        <v>401</v>
       </c>
     </row>
     <row r="78" spans="5:6" ht="24.95" customHeight="1">
       <c r="E78" s="21" t="s">
-        <v>186</v>
+        <v>94</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>187</v>
+        <v>402</v>
       </c>
     </row>
     <row r="79" spans="5:6" ht="24.95" customHeight="1">
       <c r="E79" s="21" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>189</v>
+        <v>403</v>
       </c>
     </row>
     <row r="80" spans="5:6" ht="24.95" customHeight="1">
       <c r="E80" s="21" t="s">
-        <v>190</v>
+        <v>96</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>191</v>
+        <v>404</v>
       </c>
     </row>
     <row r="81" spans="5:6" ht="24.95" customHeight="1">
       <c r="E81" s="21" t="s">
-        <v>192</v>
+        <v>97</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>193</v>
+        <v>405</v>
       </c>
     </row>
     <row r="82" spans="5:6" ht="24.95" customHeight="1">
       <c r="E82" s="21" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>193</v>
+        <v>405</v>
       </c>
     </row>
     <row r="83" spans="5:6" ht="24.95" customHeight="1">
       <c r="E83" s="21" t="s">
-        <v>198</v>
+        <v>100</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>199</v>
+        <v>406</v>
       </c>
     </row>
     <row r="84" spans="5:6" ht="24.95" customHeight="1">
       <c r="E84" s="21" t="s">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>201</v>
+        <v>407</v>
       </c>
     </row>
     <row r="85" spans="5:6" ht="24.95" customHeight="1">
       <c r="E85" s="21" t="s">
-        <v>202</v>
+        <v>102</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>203</v>
+        <v>408</v>
       </c>
     </row>
     <row r="86" spans="5:6" ht="24.95" customHeight="1">
       <c r="E86" s="21" t="s">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>205</v>
+        <v>409</v>
       </c>
     </row>
     <row r="87" spans="5:6" ht="24.95" customHeight="1">
       <c r="E87" s="21" t="s">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>207</v>
+        <v>410</v>
       </c>
     </row>
     <row r="88" spans="5:6" ht="24.95" customHeight="1">
       <c r="E88" s="21" t="s">
-        <v>210</v>
+        <v>106</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>211</v>
+        <v>411</v>
       </c>
     </row>
     <row r="89" spans="5:6" ht="24.95" customHeight="1">
       <c r="E89" s="21" t="s">
-        <v>212</v>
+        <v>107</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>213</v>
+        <v>412</v>
       </c>
     </row>
     <row r="90" spans="5:6" ht="24.95" customHeight="1">
       <c r="E90" s="21" t="s">
-        <v>214</v>
+        <v>108</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>215</v>
+        <v>413</v>
       </c>
     </row>
     <row r="91" spans="5:6" ht="24.95" customHeight="1">
       <c r="E91" s="21" t="s">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>217</v>
+        <v>414</v>
       </c>
     </row>
     <row r="92" spans="5:6" ht="24.95" customHeight="1">
       <c r="E92" s="21" t="s">
-        <v>218</v>
+        <v>110</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>219</v>
+        <v>415</v>
       </c>
     </row>
     <row r="93" spans="5:6" ht="24.95" customHeight="1">
       <c r="E93" s="21" t="s">
-        <v>220</v>
+        <v>111</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>221</v>
+        <v>416</v>
       </c>
     </row>
     <row r="94" spans="5:6" ht="24.95" customHeight="1">
       <c r="E94" s="21" t="s">
-        <v>224</v>
+        <v>113</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>225</v>
+        <v>417</v>
       </c>
     </row>
     <row r="95" spans="5:6" ht="24.95" customHeight="1">
       <c r="E95" s="21" t="s">
-        <v>226</v>
+        <v>114</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>227</v>
+        <v>418</v>
       </c>
     </row>
     <row r="96" spans="5:6" ht="24.95" customHeight="1">
       <c r="E96" s="21" t="s">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>229</v>
+        <v>419</v>
       </c>
     </row>
     <row r="97" spans="5:6" ht="24.95" customHeight="1">
       <c r="E97" s="21" t="s">
-        <v>230</v>
+        <v>116</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>231</v>
+        <v>420</v>
       </c>
     </row>
     <row r="98" spans="5:6" ht="24.95" customHeight="1">
       <c r="E98" s="21" t="s">
-        <v>232</v>
+        <v>117</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>233</v>
+        <v>421</v>
       </c>
     </row>
     <row r="99" spans="5:6" ht="24.95" customHeight="1">
       <c r="E99" s="21" t="s">
-        <v>234</v>
+        <v>118</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>235</v>
+        <v>422</v>
       </c>
     </row>
     <row r="100" spans="5:6" ht="24.95" customHeight="1">
       <c r="E100" s="21" t="s">
-        <v>238</v>
+        <v>120</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
     </row>
     <row r="101" spans="5:6" ht="24.95" customHeight="1">
       <c r="E101" s="21" t="s">
-        <v>242</v>
+        <v>122</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>31</v>
+        <v>292</v>
       </c>
     </row>
     <row r="102" spans="5:6" ht="24.95" customHeight="1">
       <c r="E102" s="21" t="s">
-        <v>246</v>
+        <v>124</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>247</v>
+        <v>423</v>
       </c>
     </row>
     <row r="103" spans="5:6" ht="24.95" customHeight="1">
       <c r="E103" s="21" t="s">
-        <v>248</v>
+        <v>125</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>249</v>
+        <v>424</v>
       </c>
     </row>
     <row r="104" spans="5:6" ht="24.95" customHeight="1">
       <c r="E104" s="21" t="s">
-        <v>252</v>
+        <v>127</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>253</v>
+        <v>425</v>
       </c>
     </row>
     <row r="105" spans="5:6" ht="24.95" customHeight="1">
       <c r="E105" s="21" t="s">
-        <v>254</v>
+        <v>128</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>249</v>
+        <v>424</v>
       </c>
     </row>
     <row r="106" spans="5:6" ht="24.95" customHeight="1">
       <c r="E106" s="21" t="s">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>258</v>
+        <v>426</v>
       </c>
     </row>
     <row r="107" spans="5:6" ht="24.95" customHeight="1">
       <c r="E107" s="21" t="s">
-        <v>261</v>
+        <v>132</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>262</v>
+        <v>427</v>
       </c>
     </row>
     <row r="108" spans="5:6" ht="24.95" customHeight="1">
       <c r="E108" s="21" t="s">
-        <v>263</v>
+        <v>133</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>264</v>
+        <v>428</v>
       </c>
     </row>
     <row r="109" spans="5:6" ht="24.95" customHeight="1">
       <c r="E109" s="21" t="s">
-        <v>265</v>
+        <v>134</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>266</v>
+        <v>429</v>
       </c>
     </row>
     <row r="110" spans="5:6" ht="24.95" customHeight="1">
       <c r="E110" s="21" t="s">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="F110" s="16" t="s">
-        <v>270</v>
+        <v>430</v>
       </c>
     </row>
     <row r="111" spans="5:6" ht="24.95" customHeight="1">
       <c r="E111" s="21" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="F111" s="16" t="s">
-        <v>272</v>
+        <v>431</v>
       </c>
     </row>
     <row r="112" spans="5:6" ht="24.95" customHeight="1">
       <c r="E112" s="21" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="F112" s="16" t="s">
-        <v>274</v>
+        <v>432</v>
       </c>
     </row>
     <row r="113" spans="5:6" ht="24.95" customHeight="1">
       <c r="E113" s="21" t="s">
-        <v>275</v>
+        <v>139</v>
       </c>
       <c r="F113" s="16" t="s">
-        <v>276</v>
+        <v>433</v>
       </c>
     </row>
     <row r="114" spans="5:6" ht="24.95" customHeight="1">
       <c r="E114" s="21" t="s">
-        <v>277</v>
+        <v>140</v>
       </c>
       <c r="F114" s="16" t="s">
-        <v>278</v>
+        <v>434</v>
       </c>
     </row>
     <row r="115" spans="5:6" ht="24.95" customHeight="1">
       <c r="E115" s="21" t="s">
-        <v>281</v>
+        <v>142</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>31</v>
+        <v>293</v>
       </c>
     </row>
     <row r="116" spans="5:6" ht="24.95" customHeight="1">
       <c r="E116" s="21" t="s">
-        <v>285</v>
+        <v>144</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>286</v>
+        <v>435</v>
       </c>
     </row>
     <row r="117" spans="5:6" ht="24.95" customHeight="1">
       <c r="E117" s="21" t="s">
-        <v>287</v>
+        <v>145</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>288</v>
+        <v>436</v>
       </c>
     </row>
     <row r="118" spans="5:6" ht="24.95" customHeight="1">
       <c r="E118" s="21" t="s">
-        <v>289</v>
+        <v>146</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>290</v>
+        <v>437</v>
       </c>
     </row>
     <row r="119" spans="5:6" ht="24.95" customHeight="1">
       <c r="E119" s="21" t="s">
-        <v>291</v>
+        <v>147</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>292</v>
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="5:6" ht="24.95" customHeight="1">
       <c r="E120" s="21" t="s">
-        <v>293</v>
+        <v>148</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>294</v>
+        <v>439</v>
       </c>
     </row>
     <row r="121" spans="5:6" ht="24.95" customHeight="1">
       <c r="E121" s="21" t="s">
-        <v>295</v>
+        <v>149</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>296</v>
+        <v>440</v>
       </c>
     </row>
     <row r="122" spans="5:6" ht="24.95" customHeight="1">
       <c r="E122" s="21" t="s">
-        <v>297</v>
+        <v>150</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>298</v>
+        <v>441</v>
       </c>
     </row>
     <row r="123" spans="5:6" ht="24.95" customHeight="1">
       <c r="E123" s="21" t="s">
-        <v>299</v>
+        <v>151</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>300</v>
+        <v>442</v>
       </c>
     </row>
     <row r="124" spans="5:6" ht="24.95" customHeight="1">
       <c r="E124" s="21" t="s">
-        <v>301</v>
+        <v>152</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>302</v>
+        <v>443</v>
       </c>
     </row>
     <row r="125" spans="5:6" ht="24.95" customHeight="1">
       <c r="E125" s="21" t="s">
-        <v>305</v>
+        <v>154</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>306</v>
+        <v>444</v>
       </c>
     </row>
     <row r="126" spans="5:6" ht="24.95" customHeight="1">
       <c r="E126" s="21" t="s">
-        <v>307</v>
+        <v>155</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>308</v>
+        <v>445</v>
       </c>
     </row>
     <row r="127" spans="5:6" ht="24.95" customHeight="1">
       <c r="E127" s="21" t="s">
-        <v>309</v>
+        <v>156</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>310</v>
+        <v>446</v>
       </c>
     </row>
     <row r="128" spans="5:6" ht="24.95" customHeight="1">
       <c r="E128" s="21" t="s">
-        <v>311</v>
+        <v>157</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>312</v>
+        <v>447</v>
       </c>
     </row>
     <row r="129" spans="5:6" ht="24.95" customHeight="1">
       <c r="E129" s="21" t="s">
-        <v>313</v>
+        <v>158</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>314</v>
+        <v>448</v>
       </c>
     </row>
     <row r="130" spans="5:6" ht="24.95" customHeight="1">
       <c r="E130" s="21" t="s">
-        <v>315</v>
+        <v>159</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>316</v>
+        <v>449</v>
       </c>
     </row>
     <row r="131" spans="5:6" ht="24.95" customHeight="1">
       <c r="E131" s="21" t="s">
-        <v>319</v>
+        <v>161</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>320</v>
+        <v>450</v>
       </c>
     </row>
     <row r="132" spans="5:6" ht="24.95" customHeight="1">
       <c r="E132" s="21" t="s">
-        <v>321</v>
+        <v>162</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>322</v>
+        <v>451</v>
       </c>
     </row>
     <row r="133" spans="5:6" ht="24.95" customHeight="1">
       <c r="E133" s="21" t="s">
-        <v>323</v>
+        <v>163</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>324</v>
+        <v>452</v>
       </c>
     </row>
     <row r="134" spans="5:6" ht="24.95" customHeight="1">
       <c r="E134" s="21" t="s">
-        <v>325</v>
+        <v>164</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>326</v>
+        <v>453</v>
       </c>
     </row>
     <row r="135" spans="5:6" ht="24.95" customHeight="1">
       <c r="E135" s="21" t="s">
-        <v>329</v>
+        <v>166</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>330</v>
+        <v>454</v>
       </c>
     </row>
     <row r="136" spans="5:6" ht="24.95" customHeight="1">
       <c r="E136" s="21" t="s">
-        <v>331</v>
+        <v>167</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>332</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="5:6" ht="24.95" customHeight="1">
       <c r="E137" s="21" t="s">
-        <v>333</v>
+        <v>168</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>334</v>
+        <v>456</v>
       </c>
     </row>
     <row r="138" spans="5:6" ht="24.95" customHeight="1">
       <c r="E138" s="21" t="s">
-        <v>335</v>
+        <v>169</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>336</v>
+        <v>457</v>
       </c>
     </row>
     <row r="139" spans="5:6" ht="24.95" customHeight="1">
       <c r="E139" s="21" t="s">
-        <v>337</v>
+        <v>170</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>338</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140" spans="5:6" ht="24.95" customHeight="1">
       <c r="E140" s="21" t="s">
-        <v>341</v>
+        <v>172</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>342</v>
+        <v>459</v>
       </c>
     </row>
     <row r="141" spans="5:6" ht="24.95" customHeight="1">
       <c r="E141" s="21" t="s">
-        <v>343</v>
+        <v>173</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>344</v>
+        <v>460</v>
       </c>
     </row>
     <row r="142" spans="5:6" ht="24.95" customHeight="1">
       <c r="E142" s="21" t="s">
-        <v>345</v>
+        <v>174</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>346</v>
+        <v>461</v>
       </c>
     </row>
     <row r="143" spans="5:6" ht="24.95" customHeight="1">
       <c r="E143" s="21" t="s">
-        <v>347</v>
+        <v>175</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>348</v>
+        <v>462</v>
       </c>
     </row>
     <row r="144" spans="5:6" ht="24.95" customHeight="1">
       <c r="E144" s="21" t="s">
-        <v>349</v>
+        <v>176</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>350</v>
+        <v>463</v>
       </c>
     </row>
     <row r="145" spans="5:6" ht="24.95" customHeight="1">
       <c r="E145" s="21" t="s">
-        <v>351</v>
+        <v>177</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>352</v>
+        <v>464</v>
       </c>
     </row>
     <row r="146" spans="5:6" ht="24.95" customHeight="1">
       <c r="E146" s="21" t="s">
-        <v>353</v>
+        <v>178</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>354</v>
+        <v>465</v>
       </c>
     </row>
     <row r="147" spans="5:6" ht="24.95" customHeight="1">
       <c r="E147" s="21" t="s">
-        <v>355</v>
+        <v>179</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>356</v>
+        <v>466</v>
       </c>
     </row>
     <row r="148" spans="5:6" ht="24.95" customHeight="1">
       <c r="E148" s="21" t="s">
-        <v>357</v>
+        <v>180</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>358</v>
+        <v>467</v>
       </c>
     </row>
     <row r="149" spans="5:6" ht="24.95" customHeight="1">
       <c r="E149" s="21" t="s">
-        <v>359</v>
+        <v>181</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>360</v>
+        <v>468</v>
       </c>
     </row>
     <row r="150" spans="5:6" ht="24.95" customHeight="1">
       <c r="E150" s="21" t="s">
-        <v>361</v>
+        <v>182</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>362</v>
+        <v>469</v>
       </c>
     </row>
     <row r="151" spans="5:6" ht="24.95" customHeight="1">
       <c r="E151" s="21" t="s">
-        <v>363</v>
+        <v>183</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>364</v>
+        <v>470</v>
       </c>
     </row>
     <row r="152" spans="5:6" ht="24.95" customHeight="1">
       <c r="E152" s="21" t="s">
-        <v>365</v>
+        <v>184</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>366</v>
+        <v>471</v>
       </c>
     </row>
     <row r="153" spans="5:6" ht="24.95" customHeight="1">
       <c r="E153" s="21" t="s">
-        <v>367</v>
+        <v>185</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>368</v>
+        <v>472</v>
       </c>
     </row>
     <row r="154" spans="5:6" ht="24.95" customHeight="1">
       <c r="E154" s="21" t="s">
-        <v>369</v>
+        <v>186</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>370</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155" spans="5:6" ht="24.95" customHeight="1">
       <c r="E155" s="21" t="s">
-        <v>371</v>
+        <v>187</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>372</v>
+        <v>474</v>
       </c>
     </row>
     <row r="156" spans="5:6" ht="24.95" customHeight="1">
       <c r="E156" s="21" t="s">
-        <v>375</v>
+        <v>189</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>376</v>
+        <v>475</v>
       </c>
     </row>
     <row r="157" spans="5:6" ht="24.95" customHeight="1">
       <c r="E157" s="21" t="s">
-        <v>377</v>
+        <v>190</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>378</v>
+        <v>476</v>
       </c>
     </row>
     <row r="158" spans="5:6" ht="24.95" customHeight="1">
       <c r="E158" s="21" t="s">
-        <v>379</v>
+        <v>191</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>380</v>
+        <v>477</v>
       </c>
     </row>
     <row r="159" spans="5:6" ht="24.95" customHeight="1">
       <c r="E159" s="21" t="s">
-        <v>381</v>
+        <v>192</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>382</v>
+        <v>478</v>
       </c>
     </row>
     <row r="160" spans="5:6" ht="24.95" customHeight="1">
       <c r="E160" s="21" t="s">
-        <v>383</v>
+        <v>193</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>384</v>
+        <v>479</v>
       </c>
     </row>
     <row r="161" spans="5:6" ht="24.95" customHeight="1">
       <c r="E161" s="21" t="s">
-        <v>385</v>
+        <v>194</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>386</v>
+        <v>480</v>
       </c>
     </row>
     <row r="162" spans="5:6" ht="24.95" customHeight="1">
       <c r="E162" s="21" t="s">
-        <v>387</v>
+        <v>195</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>388</v>
+        <v>481</v>
       </c>
     </row>
     <row r="163" spans="5:6" ht="24.95" customHeight="1">
       <c r="E163" s="21" t="s">
-        <v>391</v>
+        <v>197</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>392</v>
+        <v>482</v>
       </c>
     </row>
     <row r="164" spans="5:6" ht="24.95" customHeight="1">
       <c r="E164" s="21" t="s">
-        <v>393</v>
+        <v>198</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
     </row>
     <row r="165" spans="5:6" ht="24.95" customHeight="1">
       <c r="E165" s="21" t="s">
-        <v>395</v>
+        <v>199</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>396</v>
+        <v>484</v>
       </c>
     </row>
     <row r="166" spans="5:6" ht="24.95" customHeight="1">
       <c r="E166" s="21" t="s">
-        <v>397</v>
+        <v>200</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>398</v>
+        <v>485</v>
       </c>
     </row>
     <row r="167" spans="5:6" ht="24.95" customHeight="1">
       <c r="E167" s="21" t="s">
-        <v>399</v>
+        <v>201</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>400</v>
+        <v>486</v>
       </c>
     </row>
     <row r="168" spans="5:6" ht="24.95" customHeight="1">
       <c r="E168" s="21" t="s">
-        <v>401</v>
+        <v>202</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>402</v>
+        <v>487</v>
       </c>
     </row>
     <row r="169" spans="5:6" ht="24.95" customHeight="1">
       <c r="E169" s="21" t="s">
-        <v>403</v>
+        <v>203</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>404</v>
+        <v>488</v>
       </c>
     </row>
     <row r="170" spans="5:6" ht="24.95" customHeight="1">
       <c r="E170" s="21" t="s">
-        <v>405</v>
+        <v>204</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>406</v>
+        <v>489</v>
       </c>
     </row>
     <row r="171" spans="5:6" ht="24.95" customHeight="1">
       <c r="E171" s="21" t="s">
-        <v>407</v>
+        <v>205</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>408</v>
+        <v>490</v>
       </c>
     </row>
     <row r="172" spans="5:6" ht="24.95" customHeight="1">
       <c r="E172" s="21" t="s">
-        <v>409</v>
+        <v>206</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>410</v>
+        <v>491</v>
       </c>
     </row>
     <row r="173" spans="5:6" ht="24.95" customHeight="1">
       <c r="E173" s="21" t="s">
-        <v>411</v>
+        <v>207</v>
       </c>
       <c r="F173" s="10" t="s">
-        <v>412</v>
+        <v>492</v>
       </c>
     </row>
     <row r="174" spans="5:6" ht="24.95" customHeight="1">
       <c r="E174" s="21" t="s">
-        <v>413</v>
+        <v>208</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>414</v>
+        <v>493</v>
       </c>
     </row>
     <row r="175" spans="5:6" ht="24.95" customHeight="1">
       <c r="E175" s="21" t="s">
-        <v>417</v>
+        <v>210</v>
       </c>
       <c r="F175" s="10" t="s">
-        <v>418</v>
+        <v>494</v>
       </c>
     </row>
     <row r="176" spans="5:6" ht="24.95" customHeight="1">
       <c r="E176" s="21" t="s">
-        <v>419</v>
+        <v>211</v>
       </c>
       <c r="F176" s="10" t="s">
-        <v>420</v>
+        <v>495</v>
       </c>
     </row>
     <row r="177" spans="5:6" ht="24.95" customHeight="1">
       <c r="E177" s="21" t="s">
-        <v>421</v>
+        <v>212</v>
       </c>
       <c r="F177" s="10" t="s">
-        <v>422</v>
+        <v>496</v>
       </c>
     </row>
     <row r="178" spans="5:6" ht="24.95" customHeight="1">
       <c r="E178" s="21" t="s">
-        <v>426</v>
+        <v>214</v>
       </c>
       <c r="F178" s="10" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
     </row>
     <row r="179" spans="5:6" ht="24.95" customHeight="1">
       <c r="E179" s="21" t="s">
-        <v>428</v>
+        <v>215</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>429</v>
+        <v>498</v>
       </c>
     </row>
     <row r="180" spans="5:6" ht="24.95" customHeight="1">
       <c r="E180" s="21" t="s">
-        <v>430</v>
+        <v>216</v>
       </c>
       <c r="F180" s="10" t="s">
-        <v>431</v>
+        <v>499</v>
       </c>
     </row>
     <row r="181" spans="5:6" ht="24.95" customHeight="1">
       <c r="E181" s="21" t="s">
-        <v>432</v>
+        <v>217</v>
       </c>
       <c r="F181" s="10" t="s">
-        <v>433</v>
+        <v>500</v>
       </c>
     </row>
     <row r="182" spans="5:6" ht="24.95" customHeight="1">
       <c r="E182" s="21" t="s">
-        <v>434</v>
+        <v>218</v>
       </c>
       <c r="F182" s="10" t="s">
-        <v>435</v>
+        <v>501</v>
       </c>
     </row>
     <row r="183" spans="5:6" ht="24.95" customHeight="1">
       <c r="E183" s="21" t="s">
-        <v>436</v>
+        <v>219</v>
       </c>
       <c r="F183" s="10" t="s">
-        <v>437</v>
+        <v>502</v>
       </c>
     </row>
     <row r="184" spans="5:6" ht="24.95" customHeight="1">
       <c r="E184" s="21" t="s">
-        <v>438</v>
+        <v>220</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>439</v>
+        <v>503</v>
       </c>
     </row>
     <row r="185" spans="5:6" ht="24.95" customHeight="1">
       <c r="E185" s="21" t="s">
-        <v>440</v>
+        <v>221</v>
       </c>
       <c r="F185" s="10" t="s">
-        <v>441</v>
+        <v>504</v>
       </c>
     </row>
     <row r="186" spans="5:6" ht="24.95" customHeight="1">
       <c r="E186" s="21" t="s">
-        <v>442</v>
+        <v>222</v>
       </c>
       <c r="F186" s="10" t="s">
-        <v>443</v>
+        <v>505</v>
       </c>
     </row>
     <row r="187" spans="5:6" ht="24.95" customHeight="1">
       <c r="E187" s="21" t="s">
-        <v>444</v>
+        <v>223</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>445</v>
+        <v>506</v>
       </c>
     </row>
     <row r="188" spans="5:6" ht="24.95" customHeight="1">
       <c r="E188" s="21" t="s">
-        <v>446</v>
+        <v>224</v>
       </c>
       <c r="F188" s="10" t="s">
-        <v>447</v>
+        <v>507</v>
       </c>
     </row>
     <row r="189" spans="5:6" ht="24.95" customHeight="1">
       <c r="E189" s="21" t="s">
-        <v>448</v>
+        <v>225</v>
       </c>
       <c r="F189" s="10" t="s">
-        <v>449</v>
+        <v>508</v>
       </c>
     </row>
     <row r="190" spans="5:6" ht="24.95" customHeight="1">
       <c r="E190" s="21" t="s">
-        <v>450</v>
+        <v>226</v>
       </c>
       <c r="F190" s="10" t="s">
-        <v>451</v>
+        <v>509</v>
       </c>
     </row>
     <row r="191" spans="5:6" ht="24.95" customHeight="1">
       <c r="E191" s="21" t="s">
-        <v>452</v>
+        <v>227</v>
       </c>
       <c r="F191" s="10" t="s">
-        <v>453</v>
+        <v>510</v>
       </c>
     </row>
     <row r="192" spans="5:6" ht="24.95" customHeight="1">
       <c r="E192" s="21" t="s">
-        <v>454</v>
+        <v>228</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>455</v>
+        <v>511</v>
       </c>
     </row>
     <row r="193" spans="5:6" ht="24.95" customHeight="1">
       <c r="E193" s="21" t="s">
-        <v>456</v>
+        <v>229</v>
       </c>
       <c r="F193" s="10" t="s">
-        <v>457</v>
+        <v>512</v>
       </c>
     </row>
     <row r="194" spans="5:6" ht="24.95" customHeight="1">
       <c r="E194" s="21" t="s">
-        <v>458</v>
+        <v>230</v>
       </c>
       <c r="F194" s="10" t="s">
-        <v>459</v>
+        <v>513</v>
       </c>
     </row>
     <row r="195" spans="5:6" ht="24.95" customHeight="1">
       <c r="E195" s="21" t="s">
-        <v>460</v>
+        <v>231</v>
       </c>
       <c r="F195" s="10" t="s">
-        <v>461</v>
+        <v>514</v>
       </c>
     </row>
     <row r="196" spans="5:6" ht="24.95" customHeight="1">
       <c r="E196" s="21" t="s">
-        <v>462</v>
+        <v>232</v>
       </c>
       <c r="F196" s="10" t="s">
-        <v>463</v>
+        <v>515</v>
       </c>
     </row>
     <row r="197" spans="5:6" ht="24.95" customHeight="1">
       <c r="E197" s="21" t="s">
-        <v>464</v>
+        <v>233</v>
       </c>
       <c r="F197" s="10" t="s">
-        <v>465</v>
+        <v>516</v>
       </c>
     </row>
     <row r="198" spans="5:6" ht="24.95" customHeight="1">
       <c r="E198" s="21" t="s">
-        <v>466</v>
+        <v>234</v>
       </c>
       <c r="F198" s="10" t="s">
-        <v>467</v>
+        <v>517</v>
       </c>
     </row>
     <row r="199" spans="5:6" ht="24.95" customHeight="1">
       <c r="E199" s="21" t="s">
-        <v>468</v>
+        <v>235</v>
       </c>
       <c r="F199" s="10" t="s">
-        <v>469</v>
+        <v>518</v>
       </c>
     </row>
     <row r="200" spans="5:6" ht="24.95" customHeight="1">
       <c r="E200" s="21" t="s">
-        <v>470</v>
+        <v>236</v>
       </c>
       <c r="F200" s="10" t="s">
-        <v>471</v>
+        <v>519</v>
       </c>
     </row>
     <row r="201" spans="5:6" ht="24.95" customHeight="1">
       <c r="E201" s="21" t="s">
-        <v>472</v>
+        <v>237</v>
       </c>
       <c r="F201" s="10" t="s">
-        <v>473</v>
+        <v>520</v>
       </c>
     </row>
     <row r="202" spans="5:6" ht="24.95" customHeight="1">
       <c r="E202" s="21" t="s">
-        <v>474</v>
+        <v>238</v>
       </c>
       <c r="F202" s="10" t="s">
-        <v>475</v>
+        <v>521</v>
       </c>
     </row>
     <row r="203" spans="5:6" ht="24.95" customHeight="1">
       <c r="E203" s="21" t="s">
-        <v>478</v>
+        <v>240</v>
       </c>
       <c r="F203" s="10" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
     </row>
     <row r="204" spans="5:6" ht="24.95" customHeight="1">
       <c r="E204" s="21" t="s">
-        <v>480</v>
+        <v>241</v>
       </c>
       <c r="F204" s="10" t="s">
-        <v>481</v>
+        <v>523</v>
       </c>
     </row>
     <row r="205" spans="5:6" ht="24.95" customHeight="1">
       <c r="E205" s="21" t="s">
-        <v>482</v>
+        <v>242</v>
       </c>
       <c r="F205" s="10" t="s">
-        <v>483</v>
+        <v>524</v>
       </c>
     </row>
     <row r="206" spans="5:6" ht="24.95" customHeight="1">
       <c r="E206" s="21" t="s">
-        <v>484</v>
+        <v>243</v>
       </c>
       <c r="F206" s="10" t="s">
-        <v>485</v>
+        <v>525</v>
       </c>
     </row>
     <row r="207" spans="5:6" ht="24.95" customHeight="1">
       <c r="E207" s="21" t="s">
-        <v>486</v>
+        <v>244</v>
       </c>
       <c r="F207" s="10" t="s">
-        <v>487</v>
+        <v>526</v>
       </c>
     </row>
     <row r="208" spans="5:6" ht="24.95" customHeight="1">
       <c r="E208" s="21" t="s">
-        <v>488</v>
+        <v>245</v>
       </c>
       <c r="F208" s="10" t="s">
-        <v>489</v>
+        <v>527</v>
       </c>
     </row>
     <row r="209" spans="5:6" ht="24.95" customHeight="1">
       <c r="E209" s="21" t="s">
-        <v>490</v>
+        <v>246</v>
       </c>
       <c r="F209" s="10" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
     </row>
     <row r="210" spans="5:6" ht="24.95" customHeight="1">
       <c r="E210" s="21" t="s">
-        <v>492</v>
+        <v>247</v>
       </c>
       <c r="F210" s="10" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
     </row>
     <row r="211" spans="5:6" ht="24.95" customHeight="1">
       <c r="E211" s="21" t="s">
-        <v>494</v>
+        <v>248</v>
       </c>
       <c r="F211" s="10" t="s">
-        <v>495</v>
+        <v>530</v>
       </c>
     </row>
     <row r="212" spans="5:6" ht="24.95" customHeight="1">
       <c r="E212" s="21" t="s">
-        <v>496</v>
+        <v>249</v>
       </c>
       <c r="F212" s="10" t="s">
-        <v>497</v>
+        <v>531</v>
       </c>
     </row>
     <row r="213" spans="5:6" ht="24.95" customHeight="1">
       <c r="E213" s="21" t="s">
-        <v>498</v>
+        <v>250</v>
       </c>
       <c r="F213" s="10" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
     </row>
     <row r="214" spans="5:6" ht="24.95" customHeight="1">
       <c r="E214" s="21" t="s">
-        <v>500</v>
+        <v>251</v>
       </c>
       <c r="F214" s="10" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
     </row>
     <row r="215" spans="5:6" ht="24.95" customHeight="1">
       <c r="E215" s="21" t="s">
-        <v>504</v>
+        <v>253</v>
       </c>
       <c r="F215" s="10" t="s">
-        <v>31</v>
+        <v>294</v>
       </c>
     </row>
     <row r="216" spans="5:6" ht="24.95" customHeight="1">
       <c r="E216" s="21" t="s">
-        <v>507</v>
+        <v>255</v>
       </c>
       <c r="F216" s="10" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
     </row>
     <row r="217" spans="5:6" ht="24.95" customHeight="1">
       <c r="E217" s="21" t="s">
-        <v>509</v>
+        <v>256</v>
       </c>
       <c r="F217" s="10" t="s">
-        <v>510</v>
+        <v>535</v>
       </c>
     </row>
     <row r="218" spans="5:6" ht="24.95" customHeight="1">
       <c r="E218" s="21" t="s">
-        <v>511</v>
+        <v>257</v>
       </c>
       <c r="F218" s="10" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
     </row>
     <row r="219" spans="5:6" ht="24.95" customHeight="1">
       <c r="E219" s="21" t="s">
-        <v>513</v>
+        <v>258</v>
       </c>
       <c r="F219" s="10" t="s">
-        <v>514</v>
+        <v>537</v>
       </c>
     </row>
     <row r="220" spans="5:6" ht="24.95" customHeight="1">
       <c r="E220" s="21" t="s">
-        <v>517</v>
+        <v>260</v>
       </c>
       <c r="F220" s="10" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
     </row>
     <row r="221" spans="5:6" ht="24.95" customHeight="1">
       <c r="E221" s="21" t="s">
-        <v>519</v>
+        <v>261</v>
       </c>
       <c r="F221" s="10" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
     </row>
     <row r="222" spans="5:6" ht="24.95" customHeight="1">
       <c r="E222" s="21" t="s">
-        <v>521</v>
+        <v>262</v>
       </c>
       <c r="F222" s="10" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
     </row>
     <row r="223" spans="5:6" ht="24.95" customHeight="1">
       <c r="E223" s="21" t="s">
-        <v>525</v>
+        <v>264</v>
       </c>
       <c r="F223" s="10" t="s">
-        <v>526</v>
+        <v>541</v>
       </c>
     </row>
     <row r="224" spans="5:6" ht="24.95" customHeight="1">
       <c r="E224" s="21" t="s">
-        <v>527</v>
+        <v>265</v>
       </c>
       <c r="F224" s="10" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
     </row>
     <row r="225" spans="5:6" ht="24.95" customHeight="1">
       <c r="E225" s="21" t="s">
-        <v>529</v>
+        <v>266</v>
       </c>
       <c r="F225" s="10" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
     </row>
     <row r="226" spans="5:6" ht="24.95" customHeight="1">
       <c r="E226" s="21" t="s">
-        <v>531</v>
+        <v>267</v>
       </c>
       <c r="F226" s="10" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
     </row>
     <row r="227" spans="5:6" ht="24.95" customHeight="1">
       <c r="E227" s="21" t="s">
-        <v>533</v>
+        <v>268</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
     </row>
     <row r="228" spans="5:6" ht="24.95" customHeight="1">
       <c r="E228" s="21" t="s">
-        <v>537</v>
+        <v>270</v>
       </c>
       <c r="F228" s="10" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="229" spans="5:6" ht="24.95" customHeight="1">
       <c r="E229" s="21" t="s">
-        <v>539</v>
+        <v>271</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="230" spans="5:6" ht="24.95" customHeight="1">
       <c r="E230" s="21" t="s">
-        <v>541</v>
+        <v>272</v>
       </c>
       <c r="F230" s="7" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="231" spans="5:6" ht="24.95" customHeight="1"/>
